--- a/output/tables/mi_full_models_pooled.xlsx
+++ b/output/tables/mi_full_models_pooled.xlsx
@@ -427,31 +427,31 @@
         </is>
       </c>
       <c r="C2">
-        <v>838890735043500.9</v>
+        <v>2.766606553076068E+16</v>
       </c>
       <c r="D2">
-        <v>34.10340590304573</v>
+        <v>37.28804123180329</v>
       </c>
       <c r="E2">
-        <v>1.007614948467014</v>
+        <v>1.015311658519328</v>
       </c>
       <c r="F2">
-        <v>12.91606064622119</v>
+        <v>12.05781538122944</v>
       </c>
       <c r="G2">
-        <v>0.332143959231161</v>
+        <v>0.329897837489999</v>
       </c>
       <c r="H2">
-        <v>8.044609150020991E-18</v>
+        <v>1.503237180419744E-19</v>
       </c>
       <c r="I2">
-        <v>8.747941039994328E+46</v>
+        <v>5.091752598472987E+51</v>
       </c>
       <c r="J2">
-        <v>8.044609150020991E-18</v>
+        <v>1.503237180419744E-19</v>
       </c>
       <c r="K2">
-        <v>8.747941039994328E+46</v>
+        <v>5.091752598472987E+51</v>
       </c>
     </row>
     <row r="3">
@@ -466,31 +466,31 @@
         </is>
       </c>
       <c r="C3">
-        <v>0.8446354791586788</v>
+        <v>0.8417413994285633</v>
       </c>
       <c r="D3">
-        <v>0.2273612405510951</v>
+        <v>0.2443431276808681</v>
       </c>
       <c r="E3">
-        <v>-0.7426513415402884</v>
+        <v>-0.7050840353785236</v>
       </c>
       <c r="F3">
-        <v>13.97682304385603</v>
+        <v>12.61631691212207</v>
       </c>
       <c r="G3">
-        <v>0.4699912710662062</v>
+        <v>0.4935703267029977</v>
       </c>
       <c r="H3">
-        <v>0.5186285445773229</v>
+        <v>0.4956971087607971</v>
       </c>
       <c r="I3">
-        <v>1.375568506810654</v>
+        <v>1.429357910283602</v>
       </c>
       <c r="J3">
-        <v>0.5186285445773229</v>
+        <v>0.4956971087607971</v>
       </c>
       <c r="K3">
-        <v>1.375568506810654</v>
+        <v>1.429357910283602</v>
       </c>
     </row>
     <row r="4">
@@ -505,31 +505,31 @@
         </is>
       </c>
       <c r="C4">
-        <v>1.082156438410823</v>
+        <v>1.090763983792197</v>
       </c>
       <c r="D4">
-        <v>0.08277947738138079</v>
+        <v>0.08518230152161964</v>
       </c>
       <c r="E4">
-        <v>0.9538083001446827</v>
+        <v>1.01991084689308</v>
       </c>
       <c r="F4">
-        <v>17.5809927389627</v>
+        <v>17.40266178454178</v>
       </c>
       <c r="G4">
-        <v>0.3531119356106267</v>
+        <v>0.3217409406154322</v>
       </c>
       <c r="H4">
-        <v>0.9091410244272864</v>
+        <v>0.9116270132744394</v>
       </c>
       <c r="I4">
-        <v>1.288097804113184</v>
+        <v>1.305101813585743</v>
       </c>
       <c r="J4">
-        <v>0.9091410244272864</v>
+        <v>0.9116270132744394</v>
       </c>
       <c r="K4">
-        <v>1.288097804113184</v>
+        <v>1.305101813585743</v>
       </c>
     </row>
     <row r="5">
@@ -544,31 +544,31 @@
         </is>
       </c>
       <c r="C5">
-        <v>1.013472656645185</v>
+        <v>1.014838408243666</v>
       </c>
       <c r="D5">
-        <v>0.03057122637627817</v>
+        <v>0.03133957244547255</v>
       </c>
       <c r="E5">
-        <v>0.4377550067761216</v>
+        <v>0.4699935247777364</v>
       </c>
       <c r="F5">
-        <v>17.17431173615314</v>
+        <v>16.90279194659974</v>
       </c>
       <c r="G5">
-        <v>0.6670194954587485</v>
+        <v>0.6443664317561473</v>
       </c>
       <c r="H5">
-        <v>0.9502148994463497</v>
+        <v>0.9498793516533961</v>
       </c>
       <c r="I5">
-        <v>1.080941612645638</v>
+        <v>1.084239796405575</v>
       </c>
       <c r="J5">
-        <v>0.9502148994463497</v>
+        <v>0.9498793516533961</v>
       </c>
       <c r="K5">
-        <v>1.080941612645638</v>
+        <v>1.084239796405575</v>
       </c>
     </row>
     <row r="6">
@@ -583,31 +583,31 @@
         </is>
       </c>
       <c r="C6">
-        <v>0.9843862887172408</v>
+        <v>0.9800038798772472</v>
       </c>
       <c r="D6">
-        <v>0.04112448985463674</v>
+        <v>0.04443050764636024</v>
       </c>
       <c r="E6">
-        <v>-0.3826646649305981</v>
+        <v>-0.4546143930587224</v>
       </c>
       <c r="F6">
-        <v>15.10131461681371</v>
+        <v>13.7485460016857</v>
       </c>
       <c r="G6">
-        <v>0.7073006305966721</v>
+        <v>0.6564817740457372</v>
       </c>
       <c r="H6">
-        <v>0.9018198763205587</v>
+        <v>0.8907811719861729</v>
       </c>
       <c r="I6">
-        <v>1.07451209588339</v>
+        <v>1.078163341096489</v>
       </c>
       <c r="J6">
-        <v>0.9018198763205587</v>
+        <v>0.8907811719861729</v>
       </c>
       <c r="K6">
-        <v>1.07451209588339</v>
+        <v>1.078163341096489</v>
       </c>
     </row>
     <row r="7">
@@ -622,31 +622,31 @@
         </is>
       </c>
       <c r="C7">
-        <v>0.5685110290982613</v>
+        <v>0.5206710506349949</v>
       </c>
       <c r="D7">
-        <v>0.5438047763794651</v>
+        <v>0.5761010443044489</v>
       </c>
       <c r="E7">
-        <v>-1.038487689260228</v>
+        <v>-1.132851300695794</v>
       </c>
       <c r="F7">
-        <v>13.37606971445027</v>
+        <v>13.46970183068307</v>
       </c>
       <c r="G7">
-        <v>0.3174521355860393</v>
+        <v>0.2770396197174178</v>
       </c>
       <c r="H7">
-        <v>0.1761878438293602</v>
+        <v>0.1506448704816027</v>
       </c>
       <c r="I7">
-        <v>1.834432973249797</v>
+        <v>1.799585622150054</v>
       </c>
       <c r="J7">
-        <v>0.1761878438293602</v>
+        <v>0.1506448704816027</v>
       </c>
       <c r="K7">
-        <v>1.834432973249797</v>
+        <v>1.799585622150054</v>
       </c>
     </row>
     <row r="8">
@@ -661,31 +661,31 @@
         </is>
       </c>
       <c r="C8">
-        <v>0.9851795301060728</v>
+        <v>0.993972932592975</v>
       </c>
       <c r="D8">
-        <v>0.2320917711722205</v>
+        <v>0.2320350667526815</v>
       </c>
       <c r="E8">
-        <v>-0.06433399286684145</v>
+        <v>-0.02605340465433581</v>
       </c>
       <c r="F8">
-        <v>17.82974810316543</v>
+        <v>17.90855542893837</v>
       </c>
       <c r="G8">
-        <v>0.9494200943308401</v>
+        <v>0.9795028657589765</v>
       </c>
       <c r="H8">
-        <v>0.6047911637408111</v>
+        <v>0.610356921537614</v>
       </c>
       <c r="I8">
-        <v>1.604816281601583</v>
+        <v>1.618695808738515</v>
       </c>
       <c r="J8">
-        <v>0.6047911637408111</v>
+        <v>0.610356921537614</v>
       </c>
       <c r="K8">
-        <v>1.604816281601583</v>
+        <v>1.618695808738515</v>
       </c>
     </row>
   </sheetData>
@@ -767,31 +767,31 @@
         </is>
       </c>
       <c r="C2">
-        <v>0.2317706669320384</v>
+        <v>0.2959140161837668</v>
       </c>
       <c r="D2">
-        <v>3.076225266121512</v>
+        <v>3.18376968199996</v>
       </c>
       <c r="E2">
-        <v>-0.4752600262773616</v>
+        <v>-0.3824668472745812</v>
       </c>
       <c r="F2">
-        <v>18.46134780853808</v>
+        <v>18.24683942690312</v>
       </c>
       <c r="G2">
-        <v>0.6401761772445836</v>
+        <v>0.7065335780805783</v>
       </c>
       <c r="H2">
-        <v>0.0003658237145056509</v>
+        <v>0.0003707219658244163</v>
       </c>
       <c r="I2">
-        <v>146.8402400394196</v>
+        <v>236.2015554683365</v>
       </c>
       <c r="J2">
-        <v>0.0003658237145056509</v>
+        <v>0.0003707219658244163</v>
       </c>
       <c r="K2">
-        <v>146.8402400394196</v>
+        <v>236.2015554683365</v>
       </c>
     </row>
     <row r="3">
@@ -806,31 +806,31 @@
         </is>
       </c>
       <c r="C3">
-        <v>1.010831033721867</v>
+        <v>1.010963805614005</v>
       </c>
       <c r="D3">
-        <v>0.005775774588288839</v>
+        <v>0.00574181905012089</v>
       </c>
       <c r="E3">
-        <v>1.865169430471346</v>
+        <v>1.899073921117314</v>
       </c>
       <c r="F3">
-        <v>18.69764668440229</v>
+        <v>18.85549633554915</v>
       </c>
       <c r="G3">
-        <v>0.07793018437767903</v>
+        <v>0.07296465317951166</v>
       </c>
       <c r="H3">
-        <v>0.998671601599014</v>
+        <v>0.9988807635451343</v>
       </c>
       <c r="I3">
-        <v>1.023138514301604</v>
+        <v>1.023193011180028</v>
       </c>
       <c r="J3">
-        <v>0.998671601599014</v>
+        <v>0.9988807635451343</v>
       </c>
       <c r="K3">
-        <v>1.023138514301604</v>
+        <v>1.023193011180028</v>
       </c>
     </row>
     <row r="4">
@@ -845,31 +845,31 @@
         </is>
       </c>
       <c r="C4">
-        <v>1.757827146300871</v>
+        <v>1.890643562793229</v>
       </c>
       <c r="D4">
-        <v>0.5360807497071387</v>
+        <v>0.5519410170687293</v>
       </c>
       <c r="E4">
-        <v>1.052226685394087</v>
+        <v>1.153958957260234</v>
       </c>
       <c r="F4">
-        <v>17.03295748981245</v>
+        <v>16.30604571315704</v>
       </c>
       <c r="G4">
-        <v>0.3073950533472399</v>
+        <v>0.2651506825045422</v>
       </c>
       <c r="H4">
-        <v>0.5673457568533246</v>
+        <v>0.5878031691732049</v>
       </c>
       <c r="I4">
-        <v>5.446337156745683</v>
+        <v>6.081173544129336</v>
       </c>
       <c r="J4">
-        <v>0.5673457568533246</v>
+        <v>0.5878031691732049</v>
       </c>
       <c r="K4">
-        <v>5.446337156745683</v>
+        <v>6.081173544129336</v>
       </c>
     </row>
     <row r="5">
@@ -884,31 +884,31 @@
         </is>
       </c>
       <c r="C5">
-        <v>0.977053137374994</v>
+        <v>0.9742385025828484</v>
       </c>
       <c r="D5">
-        <v>0.03426845598792194</v>
+        <v>0.03572045745961159</v>
       </c>
       <c r="E5">
-        <v>-0.6774229956696577</v>
+        <v>-0.730649549018439</v>
       </c>
       <c r="F5">
-        <v>18.51132688017116</v>
+        <v>18.24292027636975</v>
       </c>
       <c r="G5">
-        <v>0.5065165553606807</v>
+        <v>0.474273242787674</v>
       </c>
       <c r="H5">
-        <v>0.9093117256687067</v>
+        <v>0.9038666259303371</v>
       </c>
       <c r="I5">
-        <v>1.049841112026003</v>
+        <v>1.050089286058033</v>
       </c>
       <c r="J5">
-        <v>0.9093117256687067</v>
+        <v>0.9038666259303371</v>
       </c>
       <c r="K5">
-        <v>1.049841112026003</v>
+        <v>1.050089286058033</v>
       </c>
     </row>
     <row r="6">
@@ -923,31 +923,31 @@
         </is>
       </c>
       <c r="C6">
-        <v>1.316090607650084</v>
+        <v>1.329874988772991</v>
       </c>
       <c r="D6">
-        <v>0.4684989584663241</v>
+        <v>0.5031116799531242</v>
       </c>
       <c r="E6">
-        <v>0.5862674321200161</v>
+        <v>0.5666434626180844</v>
       </c>
       <c r="F6">
-        <v>14.56675329034701</v>
+        <v>14.80439075742682</v>
       </c>
       <c r="G6">
-        <v>0.566670249576944</v>
+        <v>0.5794465440768753</v>
       </c>
       <c r="H6">
-        <v>0.4835941656995046</v>
+        <v>0.4545226133845285</v>
       </c>
       <c r="I6">
-        <v>3.581710885695536</v>
+        <v>3.891043995797294</v>
       </c>
       <c r="J6">
-        <v>0.4835941656995046</v>
+        <v>0.4545226133845285</v>
       </c>
       <c r="K6">
-        <v>3.581710885695536</v>
+        <v>3.891043995797294</v>
       </c>
     </row>
     <row r="7">
@@ -962,31 +962,31 @@
         </is>
       </c>
       <c r="C7">
-        <v>1.007667054993451</v>
+        <v>0.9277731574295517</v>
       </c>
       <c r="D7">
-        <v>1.022950674974072</v>
+        <v>1.054079579242623</v>
       </c>
       <c r="E7">
-        <v>0.007466452379626832</v>
+        <v>-0.07112178243294848</v>
       </c>
       <c r="F7">
-        <v>14.65146650306277</v>
+        <v>13.90294727454531</v>
       </c>
       <c r="G7">
-        <v>0.9941434029365426</v>
+        <v>0.944313784018856</v>
       </c>
       <c r="H7">
-        <v>0.1133521283388742</v>
+        <v>0.09659528365541281</v>
       </c>
       <c r="I7">
-        <v>8.957863505514313</v>
+        <v>8.911025456661267</v>
       </c>
       <c r="J7">
-        <v>0.1133521283388742</v>
+        <v>0.09659528365541281</v>
       </c>
       <c r="K7">
-        <v>8.957863505514313</v>
+        <v>8.911025456661267</v>
       </c>
     </row>
   </sheetData>
@@ -1068,31 +1068,31 @@
         </is>
       </c>
       <c r="C2">
-        <v>132.4719405259077</v>
+        <v>243.1003689769828</v>
       </c>
       <c r="D2">
-        <v>3.778013493550949</v>
+        <v>3.535873804507223</v>
       </c>
       <c r="E2">
-        <v>1.293370407947231</v>
+        <v>1.553639836387123</v>
       </c>
       <c r="F2">
-        <v>22.14523997331872</v>
+        <v>22.08241743713067</v>
       </c>
       <c r="G2">
-        <v>0.2092123135400022</v>
+        <v>0.1344861479983948</v>
       </c>
       <c r="H2">
-        <v>0.05256150440597236</v>
+        <v>0.1591524752737664</v>
       </c>
       <c r="I2">
-        <v>333872.0081365408</v>
+        <v>371328.1197486127</v>
       </c>
       <c r="J2">
-        <v>0.05256150440597236</v>
+        <v>0.1591524752737664</v>
       </c>
       <c r="K2">
-        <v>333872.0081365408</v>
+        <v>371328.1197486127</v>
       </c>
     </row>
     <row r="3">
@@ -1107,31 +1107,31 @@
         </is>
       </c>
       <c r="C3">
-        <v>0.8770257520436526</v>
+        <v>0.8997003833095336</v>
       </c>
       <c r="D3">
-        <v>0.08038614352774021</v>
+        <v>0.06326582166846589</v>
       </c>
       <c r="E3">
-        <v>-1.632357487157994</v>
+        <v>-1.670625240141957</v>
       </c>
       <c r="F3">
-        <v>21.98128803652613</v>
+        <v>22.08078046869509</v>
       </c>
       <c r="G3">
-        <v>0.1168487541845839</v>
+        <v>0.1089112948347575</v>
       </c>
       <c r="H3">
-        <v>0.7423475049875571</v>
+        <v>0.7890931237115157</v>
       </c>
       <c r="I3">
-        <v>1.036137610189216</v>
+        <v>1.025811473201042</v>
       </c>
       <c r="J3">
-        <v>0.7423475049875571</v>
+        <v>0.7890931237115157</v>
       </c>
       <c r="K3">
-        <v>1.036137610189216</v>
+        <v>1.025811473201042</v>
       </c>
     </row>
     <row r="4">
@@ -1142,35 +1142,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Peak_StO2_post_vascular_occlusion</t>
+          <t>rate_of_deoxygenation</t>
         </is>
       </c>
       <c r="C4">
-        <v>1.032042523324424</v>
+        <v>0.6770250712697189</v>
       </c>
       <c r="D4">
-        <v>0.0565962799078889</v>
+        <v>6.859403657946469</v>
       </c>
       <c r="E4">
-        <v>0.5572781644577743</v>
+        <v>-0.05686310258312202</v>
       </c>
       <c r="F4">
-        <v>21.92530251557547</v>
+        <v>22.04468903911133</v>
       </c>
       <c r="G4">
-        <v>0.5829824883294512</v>
+        <v>0.9551665101718974</v>
       </c>
       <c r="H4">
-        <v>0.9177256228721576</v>
+        <v>4.500497705311259E-07</v>
       </c>
       <c r="I4">
-        <v>1.160599359334025</v>
+        <v>1018471.682780397</v>
       </c>
       <c r="J4">
-        <v>0.9177256228721576</v>
+        <v>4.500497705311259E-07</v>
       </c>
       <c r="K4">
-        <v>1.160599359334025</v>
+        <v>1018471.682780397</v>
       </c>
     </row>
   </sheetData>
@@ -1180,7 +1180,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1252,31 +1252,31 @@
         </is>
       </c>
       <c r="C2">
-        <v>1.284318441653661</v>
+        <v>1.374051551800795</v>
       </c>
       <c r="D2">
-        <v>2.810789872457411</v>
+        <v>2.538991623722392</v>
       </c>
       <c r="E2">
-        <v>0.0890241510008882</v>
+        <v>0.125153509618957</v>
       </c>
       <c r="F2">
-        <v>17.59236800326812</v>
+        <v>19.29490908543382</v>
       </c>
       <c r="G2">
-        <v>0.9300683555529151</v>
+        <v>0.9016968058925793</v>
       </c>
       <c r="H2">
-        <v>0.003465683422486684</v>
+        <v>0.006799441869753869</v>
       </c>
       <c r="I2">
-        <v>475.9447585054274</v>
+        <v>277.6724477055521</v>
       </c>
       <c r="J2">
-        <v>0.003465683422486684</v>
+        <v>0.006799441869753869</v>
       </c>
       <c r="K2">
-        <v>475.9447585054274</v>
+        <v>277.6724477055521</v>
       </c>
     </row>
     <row r="3">
@@ -1291,109 +1291,31 @@
         </is>
       </c>
       <c r="C3">
-        <v>0.70598336820812</v>
+        <v>0.6634144664946261</v>
       </c>
       <c r="D3">
-        <v>1.0422237173791</v>
+        <v>1.016767105028232</v>
       </c>
       <c r="E3">
-        <v>-0.3340584115863189</v>
+        <v>-0.4035883380602682</v>
       </c>
       <c r="F3">
-        <v>17.68437941559726</v>
+        <v>19.09803870694624</v>
       </c>
       <c r="G3">
-        <v>0.7422643381618588</v>
+        <v>0.6909985211398476</v>
       </c>
       <c r="H3">
-        <v>0.07881917901243717</v>
+        <v>0.07904529863738527</v>
       </c>
       <c r="I3">
-        <v>6.323492865966486</v>
+        <v>5.567930818673519</v>
       </c>
       <c r="J3">
-        <v>0.07881917901243717</v>
+        <v>0.07904529863738527</v>
       </c>
       <c r="K3">
-        <v>6.323492865966486</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Total_vessel_density</t>
-        </is>
-      </c>
-      <c r="C4">
-        <v>1.101809563168841</v>
-      </c>
-      <c r="D4">
-        <v>0.2612656855286608</v>
-      </c>
-      <c r="E4">
-        <v>0.3710930710610704</v>
-      </c>
-      <c r="F4">
-        <v>14.8159188063225</v>
-      </c>
-      <c r="G4">
-        <v>0.7158208447897095</v>
-      </c>
-      <c r="H4">
-        <v>0.6309529620039845</v>
-      </c>
-      <c r="I4">
-        <v>1.9240488381805</v>
-      </c>
-      <c r="J4">
-        <v>0.6309529620039845</v>
-      </c>
-      <c r="K4">
-        <v>1.9240488381805</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Perfused_vessel_density</t>
-        </is>
-      </c>
-      <c r="C5">
-        <v>0.799504344135372</v>
-      </c>
-      <c r="D5">
-        <v>0.299183408863647</v>
-      </c>
-      <c r="E5">
-        <v>-0.7479135089996818</v>
-      </c>
-      <c r="F5">
-        <v>11.30893614820934</v>
-      </c>
-      <c r="G5">
-        <v>0.4697799962137046</v>
-      </c>
-      <c r="H5">
-        <v>0.4147524465718058</v>
-      </c>
-      <c r="I5">
-        <v>1.541177638793424</v>
-      </c>
-      <c r="J5">
-        <v>0.4147524465718058</v>
-      </c>
-      <c r="K5">
-        <v>1.541177638793424</v>
+        <v>5.567930818673519</v>
       </c>
     </row>
   </sheetData>
@@ -1403,7 +1325,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1480,16 +1402,16 @@
         </is>
       </c>
       <c r="D2">
-        <v>14269962.38057982</v>
+        <v>43203305.19980987</v>
       </c>
       <c r="E2">
-        <v>0.0001147344007198337</v>
+        <v>9.811123480322153E-05</v>
       </c>
       <c r="F2">
-        <v>9.428571385336634</v>
+        <v>11.3749999924712</v>
       </c>
       <c r="G2">
-        <v>0.9999108462459361</v>
+        <v>0.9999234181149923</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -1520,19 +1442,19 @@
         </is>
       </c>
       <c r="C3">
-        <v>0.02326349920623029</v>
+        <v>9.910565675314065E-10</v>
       </c>
       <c r="D3">
-        <v>103914.3341762786</v>
+        <v>292978.4382510229</v>
       </c>
       <c r="E3">
-        <v>-3.619202041979694E-05</v>
+        <v>-7.076373819769476E-05</v>
       </c>
       <c r="F3">
-        <v>9.428571378601191</v>
+        <v>11.37499999355787</v>
       </c>
       <c r="G3">
-        <v>0.9999718771835271</v>
+        <v>0.9999447645269495</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -1563,19 +1485,19 @@
         </is>
       </c>
       <c r="C4">
-        <v>46.50856662703075</v>
+        <v>90.62802295849582</v>
       </c>
       <c r="D4">
-        <v>49934.92243015811</v>
+        <v>65826.84644031776</v>
       </c>
       <c r="E4">
-        <v>7.689281042809174E-05</v>
+        <v>6.846391272120252E-05</v>
       </c>
       <c r="F4">
-        <v>9.428571394016725</v>
+        <v>11.37499998435898</v>
       </c>
       <c r="G4">
-        <v>0.9999402508517365</v>
+        <v>0.9999465596829321</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -1606,19 +1528,19 @@
         </is>
       </c>
       <c r="C5">
-        <v>1.72251104786127</v>
+        <v>2.46856248547242</v>
       </c>
       <c r="D5">
-        <v>18001.60866498605</v>
+        <v>58537.91937277903</v>
       </c>
       <c r="E5">
-        <v>3.020747466838826E-05</v>
+        <v>1.543676306252652E-05</v>
       </c>
       <c r="F5">
-        <v>9.428571394901274</v>
+        <v>11.37499999715825</v>
       </c>
       <c r="G5">
-        <v>0.9999765274428878</v>
+        <v>0.9999879506519499</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -1649,19 +1571,19 @@
         </is>
       </c>
       <c r="C6">
-        <v>0.4925952865833289</v>
+        <v>0.09814089713666606</v>
       </c>
       <c r="D6">
-        <v>17591.13168275327</v>
+        <v>36023.91604206437</v>
       </c>
       <c r="E6">
-        <v>-4.025138203484829E-05</v>
+        <v>-6.443916603222513E-05</v>
       </c>
       <c r="F6">
-        <v>9.428571398244136</v>
+        <v>11.3749999820989</v>
       </c>
       <c r="G6">
-        <v>0.9999687228782308</v>
+        <v>0.9999497012465721</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -1692,19 +1614,19 @@
         </is>
       </c>
       <c r="C7">
-        <v>5.997745158505768E-14</v>
+        <v>2.703193800284142E-26</v>
       </c>
       <c r="D7">
-        <v>250012.3823640462</v>
+        <v>434532.0678026613</v>
       </c>
       <c r="E7">
-        <v>-0.0001217731994806015</v>
+        <v>-0.0001354854631387971</v>
       </c>
       <c r="F7">
-        <v>9.428571410224754</v>
+        <v>11.37499998861513</v>
       </c>
       <c r="G7">
-        <v>0.9999053767849277</v>
+        <v>0.9998942452190861</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -1735,19 +1657,19 @@
         </is>
       </c>
       <c r="C8">
-        <v>0.1382803998160687</v>
+        <v>14.9384096537038</v>
       </c>
       <c r="D8">
-        <v>153012.2851357646</v>
+        <v>994897.4119768033</v>
       </c>
       <c r="E8">
-        <v>-1.293014982964314E-05</v>
+        <v>2.71780355703618E-06</v>
       </c>
       <c r="F8">
-        <v>9.428571385227098</v>
+        <v>11.37499999948328</v>
       </c>
       <c r="G8">
-        <v>0.9999899526960228</v>
+        <v>0.9999978785862775</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -1778,19 +1700,19 @@
         </is>
       </c>
       <c r="C9">
-        <v>1.428628173645567</v>
+        <v>1.576034900581856</v>
       </c>
       <c r="D9">
-        <v>3051.30275763917</v>
+        <v>3204.975055794755</v>
       </c>
       <c r="E9">
-        <v>0.0001169056934152755</v>
+        <v>0.0001419393687346286</v>
       </c>
       <c r="F9">
-        <v>9.428571402242371</v>
+        <v>11.37499997351423</v>
       </c>
       <c r="G9">
-        <v>0.9999091590545333</v>
+        <v>0.999889207546769</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -1821,19 +1743,19 @@
         </is>
       </c>
       <c r="C10">
-        <v>0.412533721504521</v>
+        <v>264285.0953837544</v>
       </c>
       <c r="D10">
-        <v>557804.2238422821</v>
+        <v>370555.070272584</v>
       </c>
       <c r="E10">
-        <v>-1.58736217762518E-06</v>
+        <v>3.369211409527152E-05</v>
       </c>
       <c r="F10">
-        <v>9.428571425011841</v>
+        <v>11.37499997834816</v>
       </c>
       <c r="G10">
-        <v>0.999998766548684</v>
+        <v>0.9999737012217165</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -1864,19 +1786,19 @@
         </is>
       </c>
       <c r="C11">
-        <v>1.329273967143434</v>
+        <v>0.1339224202347137</v>
       </c>
       <c r="D11">
-        <v>204540.6578834208</v>
+        <v>357549.4407964558</v>
       </c>
       <c r="E11">
-        <v>1.391571273708356E-06</v>
+        <v>-5.622983483580144E-06</v>
       </c>
       <c r="F11">
-        <v>9.428571414064525</v>
+        <v>11.37499999384892</v>
       </c>
       <c r="G11">
-        <v>0.999998918686962</v>
+        <v>0.9999956109137129</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -1907,19 +1829,19 @@
         </is>
       </c>
       <c r="C12">
-        <v>2760.479328329619</v>
+        <v>0.0001890633151890571</v>
       </c>
       <c r="D12">
-        <v>978618.9998074764</v>
+        <v>1185645.424329762</v>
       </c>
       <c r="E12">
-        <v>8.0962658755611E-06</v>
+        <v>-7.231022379942254E-06</v>
       </c>
       <c r="F12">
-        <v>9.428571418688019</v>
+        <v>11.37499998508321</v>
       </c>
       <c r="G12">
-        <v>0.9999937088397727</v>
+        <v>0.9999943557399267</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -1950,19 +1872,19 @@
         </is>
       </c>
       <c r="C13">
-        <v>0.1704375780197246</v>
+        <v>1.303158506770747</v>
       </c>
       <c r="D13">
-        <v>45705.8253477835</v>
+        <v>74928.83154840568</v>
       </c>
       <c r="E13">
-        <v>-3.871248680340803E-05</v>
+        <v>3.53389920585154E-06</v>
       </c>
       <c r="F13">
-        <v>9.428571393806582</v>
+        <v>11.37499999383108</v>
       </c>
       <c r="G13">
-        <v>0.9999699186685639</v>
+        <v>0.9999972415731631</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -1989,23 +1911,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Peak_StO2_post_vascular_occlusion</t>
+          <t>rate_of_deoxygenation</t>
         </is>
       </c>
       <c r="C14">
-        <v>0.595701133636023</v>
+        <v>6.909479468512413E+295</v>
       </c>
       <c r="D14">
-        <v>32742.61392308538</v>
+        <v>8785997.429345479</v>
       </c>
       <c r="E14">
-        <v>-1.582085634746191E-05</v>
+        <v>7.753194810446923E-05</v>
       </c>
       <c r="F14">
-        <v>9.428571394891133</v>
+        <v>11.37499999437422</v>
       </c>
       <c r="G14">
-        <v>0.9999877064879371</v>
+        <v>0.9999394815206435</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -2036,19 +1958,19 @@
         </is>
       </c>
       <c r="C15">
-        <v>7.485203874609175E-11</v>
+        <v>6.455617085975471E-27</v>
       </c>
       <c r="D15">
-        <v>1024282.374958065</v>
+        <v>1579018.407336307</v>
       </c>
       <c r="E15">
-        <v>-2.276277356488895E-05</v>
+        <v>-3.819135141983729E-05</v>
       </c>
       <c r="F15">
-        <v>9.428571420805273</v>
+        <v>11.37499999309591</v>
       </c>
       <c r="G15">
-        <v>0.9999823123081795</v>
+        <v>0.9999701892887912</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -2062,92 +1984,6 @@
         <v>0</v>
       </c>
       <c r="K15" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Total_vessel_density</t>
-        </is>
-      </c>
-      <c r="C16">
-        <v>1.548477754445891E-07</v>
-      </c>
-      <c r="D16">
-        <v>184761.0805775531</v>
-      </c>
-      <c r="E16">
-        <v>-8.487081395868564E-05</v>
-      </c>
-      <c r="F16">
-        <v>9.428571402140632</v>
-      </c>
-      <c r="G16">
-        <v>0.999934051586655</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Perfused_vessel_density</t>
-        </is>
-      </c>
-      <c r="C17">
-        <v>90.04548063568379</v>
-      </c>
-      <c r="D17">
-        <v>363952.4026325365</v>
-      </c>
-      <c r="E17">
-        <v>1.236511931377198E-05</v>
-      </c>
-      <c r="F17">
-        <v>9.428571414403457</v>
-      </c>
-      <c r="G17">
-        <v>0.9999903917499713</v>
-      </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17" t="inlineStr">
         <is>
           <t>Inf</t>
         </is>
